--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -2344,12 +2344,12 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66818</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67446</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66817</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67445</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66816</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67444</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66815</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67443</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66814</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67442</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66813</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67441</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66812</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67440</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66811</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67439</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66810</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67438</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66809</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67437</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66808</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67435</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66807</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67428</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66806</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67436</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66805</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67434</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66803</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67432</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66804</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67433</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66802</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67430</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified. | Ignored older duplicate: 2026-08-16 | Rastriya Banijya Bank Limited has published a notice regarding new interest rate on loan which is going to be effective from Bhadra 01, 2083</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66800</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67429</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66799</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67427</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66798</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67426</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66797</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67425</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66796</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67424</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67049</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67423</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66794</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67422</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66793</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67421</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66792</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67420</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66791</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67419</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66790</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67418</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66789</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67417</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67039</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67416</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66787</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67415</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66786</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67414</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=66785</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67413</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">

--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -2408,12 +2408,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67444</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67385</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document could not be read; all rates marked Not specified. | Ignored older duplicate: 2026-09-16 | Everest Bank Limited has published a notice regarding new interest rate on deposit and loan products which is going to be effective from Ashwin 01, 2083</t>
         </is>
       </c>
     </row>

--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -2359,7 +2359,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb454610&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003bc9d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified. | Ignored older duplicate: 2026-09-16 | Everest Bank Limited has published a notice regarding new interest rate on deposit and loan products which is going to be effective from Ashwin 01, 2083</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003b8090&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)')) | Ignored older duplicate: 2026-09-16 | Everest Bank Limited has published a notice regarding new interest rate on deposit and loan products which is going to be effective from Ashwin 01, 2083</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fbe2b650&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fbeb69d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6006a5d50&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb600692810&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb60023b810&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb60020f990&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb3a8950&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb370cd0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb2c3f50&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb3b0190&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb98cdd0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb2f33d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6008644d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb2c0f90&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb4565d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003c9b50&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb600462290&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb60028c4d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003592d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003bba10&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb2f7c10&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb3489d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb60015a610&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003793d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003e36d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb600603ad0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb600288910&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb60012e350&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb600731a50&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fbe83690&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
         </is>
       </c>
     </row>

--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -2359,7 +2359,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb454610&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003bc9d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003b8090&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)')) | Ignored older duplicate: 2026-09-16 | Everest Bank Limited has published a notice regarding new interest rate on deposit and loan products which is going to be effective from Ashwin 01, 2083</t>
+          <t>Source document could not be read; all rates marked Not specified. | Ignored older duplicate: 2026-09-16 | Everest Bank Limited has published a notice regarding new interest rate on deposit and loan products which is going to be effective from Ashwin 01, 2083</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fbe2b650&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fbeb69d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6006a5d50&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb600692810&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb60023b810&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb60020f990&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb3a8950&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb370cd0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb2c3f50&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb3b0190&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb98cdd0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb2f33d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6008644d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb2c0f90&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb4565d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003c9b50&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb600462290&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb60028c4d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003592d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003bba10&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb2f7c10&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fb3489d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb60015a610&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003793d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb6003e36d0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb600603ad0&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb600288910&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb60012e350&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb600731a50&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Source document issue encountered: HTTPSConnectionPool(host='images.merolagani.com', port=443): Max retries exceeded with url: /content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x7fb5fbe83690&gt;, 'Connection to images.merolagani.com timed out. (connect timeout=90)'))</t>
+          <t>Source document could not be read; all rates marked Not specified.</t>
         </is>
       </c>
     </row>

--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -2952,12 +2952,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67426</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67526</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Source document could not be read; all rates marked Not specified. | Ignored older duplicate: 2026-09-16 | Standard Chartered Bank Nepal Limited has published a notice regarding new interest rate on deposit and lending rates which is going to be effective from Ashwin 01, 2083</t>
         </is>
       </c>
     </row>

--- a/output/interest_rate_report.xlsx
+++ b/output/interest_rate_report.xlsx
@@ -2354,12 +2354,12 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2386,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified. | Ignored older duplicate: 2026-09-16 | Everest Bank Limited has published a notice regarding new interest rate on deposit and loan products which is going to be effective from Ashwin 01, 2083</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text. | Ignored older duplicate: 2026-09-16 | Everest Bank Limited has published a notice regarding new interest rate on deposit and loan products which is going to be effective from Ashwin 01, 2083</t>
         </is>
       </c>
     </row>
@@ -2450,12 +2450,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2738,12 +2738,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2866,12 +2866,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2898,12 +2898,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified. | Ignored older duplicate: 2026-09-16 | Standard Chartered Bank Nepal Limited has published a notice regarding new interest rate on deposit and lending rates which is going to be effective from Ashwin 01, 2083</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text. | Ignored older duplicate: 2026-09-16 | Standard Chartered Bank Nepal Limited has published a notice regarding new interest rate on deposit and lending rates which is going to be effective from Ashwin 01, 2083</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -3026,12 +3026,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -3058,12 +3058,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -3090,12 +3090,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -3154,12 +3154,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -3186,12 +3186,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -3218,12 +3218,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -3250,12 +3250,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
@@ -3378,12 +3378,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://images.merolagani.com//content/bigyapan/f4ac68d3-5980-4c7e-9896-932b1c160de4.gif</t>
+          <t>https://images.merolagani.com/Content/images/payment-partners/Ncell-new.png</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Source document could not be read; all rates marked Not specified.</t>
+          <t>Saving deposit rate not specified/readable in extracted text. | Call deposit rate not specified/readable in extracted text. | Individual FD &lt;1 Year not specified/readable in extracted text. | Individual FD 1 Year not specified/readable in extracted text. | Individual FD &gt;1 Year not specified/readable in extracted text. | Institution FD &lt;1 Year not specified/readable in extracted text. | Institution FD 1 Year not specified/readable in extracted text. | Institution FD &gt;1 Year not specified/readable in extracted text.</t>
         </is>
       </c>
     </row>
